--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104537_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104537_W9.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.662</v>
+        <v>11.2613</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5527</v>
+        <v>7.8014</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1093</v>
+        <v>3.4599</v>
       </c>
       <c r="G2" t="n">
-        <v>7.9667</v>
+        <v>7.9581</v>
       </c>
       <c r="H2" t="n">
-        <v>5.8369</v>
+        <v>5.8279</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1298</v>
+        <v>2.1302</v>
       </c>
       <c r="J2" t="n">
-        <v>7.9869</v>
+        <v>7.9562</v>
       </c>
       <c r="K2" t="n">
-        <v>5.524</v>
+        <v>5.4986</v>
       </c>
       <c r="L2" t="n">
-        <v>2.4629</v>
+        <v>2.4576</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0203</v>
+        <v>0.0019</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3129</v>
+        <v>0.3294</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9222</v>
+        <v>1.5308</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0344</v>
+        <v>0.3295</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8878</v>
+        <v>1.2013</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.2023</v>
+        <v>7.2689</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2771</v>
+        <v>7.0088</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9252</v>
+        <v>0.26</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5047</v>
+        <v>7.9052</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2035</v>
+        <v>2.2748</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3012</v>
+        <v>5.6304</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2455</v>
+        <v>8.5466</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9843</v>
+        <v>2.2613</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2612</v>
+        <v>6.2854</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2592</v>
+        <v>-0.6414</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2192</v>
+        <v>0.0135</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04</v>
+        <v>-0.6549</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3081</v>
+        <v>-0.1811</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4567</v>
+        <v>-0.351</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8514</v>
+        <v>0.1699</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5748</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5748</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.6552</v>
+        <v>6.6871</v>
       </c>
       <c r="E4" t="n">
-        <v>6.8685</v>
+        <v>3.896</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2134</v>
+        <v>2.7911</v>
       </c>
       <c r="G4" t="n">
-        <v>7.9146</v>
+        <v>2.503</v>
       </c>
       <c r="H4" t="n">
-        <v>2.277</v>
+        <v>2.1975</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6375</v>
+        <v>0.3056</v>
       </c>
       <c r="J4" t="n">
-        <v>8.5825</v>
+        <v>2.2289</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2787</v>
+        <v>1.9683</v>
       </c>
       <c r="L4" t="n">
-        <v>6.3038</v>
+        <v>0.2607</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.668</v>
+        <v>0.2741</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0017</v>
+        <v>0.2292</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6663</v>
+        <v>0.0449</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8057</v>
+        <v>0.8002</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5383</v>
+        <v>0.1043</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2674</v>
+        <v>0.6959</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.5628</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.5628</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7483</v>
+        <v>4.1498</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9381</v>
+        <v>4.154</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1898</v>
+        <v>-0.0042</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4417</v>
+        <v>3.4451</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4097</v>
+        <v>3.4092</v>
       </c>
       <c r="I5" t="n">
-        <v>0.032</v>
+        <v>0.0359</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3338</v>
+        <v>4.317</v>
       </c>
       <c r="K5" t="n">
-        <v>3.0651</v>
+        <v>3.0509</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8921</v>
+        <v>-0.8719</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5762</v>
+        <v>-0.1846</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5565</v>
+        <v>-0.3207</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0197</v>
+        <v>0.1361</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8907</v>
+        <v>2.068</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6112</v>
+        <v>1.6949</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2795</v>
+        <v>0.3731</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8172</v>
+        <v>1.8137</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4244</v>
+        <v>-0.4141</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2416</v>
+        <v>2.2279</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8216</v>
+        <v>1.7974</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5959</v>
+        <v>-0.6</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4175</v>
+        <v>2.3974</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0044</v>
+        <v>0.0164</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1715</v>
+        <v>0.1859</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2214</v>
+        <v>-0.0417</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3297</v>
+        <v>-0.2115</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1083</v>
+        <v>0.1699</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0438</v>
+        <v>1.1295</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4687</v>
+        <v>-1.0701</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5125</v>
+        <v>2.1996</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5726</v>
+        <v>0.5709</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1616</v>
+        <v>1.1577</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4306</v>
+        <v>0.4098</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4707</v>
+        <v>0.4547</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.04</v>
+        <v>-0.0449</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1419</v>
+        <v>0.1611</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6566</v>
+        <v>0.7376</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7652</v>
+        <v>-0.3417</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4218</v>
+        <v>1.0793</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2509</v>
+        <v>0.8814</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6732</v>
+        <v>-0.3486</v>
       </c>
       <c r="F8" t="n">
-        <v>0.924</v>
+        <v>1.23</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2001</v>
+        <v>-0.2091</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8369</v>
+        <v>0.8386</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.037</v>
+        <v>-1.0477</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1447</v>
+        <v>-0.1674</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4604</v>
+        <v>0.4514</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6052</v>
+        <v>-0.6188</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0554</v>
+        <v>-0.0417</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3764</v>
+        <v>0.3871</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4564</v>
+        <v>0.18</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4869</v>
+        <v>-0.1326</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0305</v>
+        <v>0.3126</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0254</v>
+        <v>0.1432</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0672</v>
+        <v>0.002</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0418</v>
+        <v>0.1411</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0185</v>
+        <v>-0.0137</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1544</v>
+        <v>-0.1523</v>
       </c>
       <c r="I9" t="n">
-        <v>0.136</v>
+        <v>0.1387</v>
       </c>
       <c r="J9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0717</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.0854</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O9" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2338</v>
+        <v>-0.0708</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1391</v>
+        <v>-0.0697</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1975</v>
+        <v>-0.2564</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.436</v>
+        <v>-1.3334</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2385</v>
+        <v>1.077</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.907</v>
+        <v>-0.8976</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3938</v>
+        <v>0.4044</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3008</v>
+        <v>-1.302</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0418</v>
+        <v>-0.0534</v>
       </c>
       <c r="K10" t="n">
-        <v>0.71</v>
+        <v>0.7067</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7517</v>
+        <v>-0.7601</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8653</v>
+        <v>-0.8442</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>0.029</v>
+        <v>-0.0417</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2601</v>
+        <v>-0.1418</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2891</v>
+        <v>0.1002</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5457</v>
+        <v>-0.4912</v>
       </c>
       <c r="E11" t="n">
-        <v>0.015</v>
+        <v>-0.0089</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5607</v>
+        <v>-0.4822</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8578</v>
+        <v>1.8585</v>
       </c>
       <c r="H11" t="n">
         <v>0.2958</v>
       </c>
       <c r="I11" t="n">
-        <v>1.562</v>
+        <v>1.5626</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4704</v>
+        <v>2.4581</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0448</v>
+        <v>0.0377</v>
       </c>
       <c r="L11" t="n">
-        <v>2.4256</v>
+        <v>2.4204</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6126</v>
+        <v>-0.5997</v>
       </c>
       <c r="N11" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4301</v>
+        <v>-0.3692</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0823</v>
+        <v>-0.0207</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7513</v>
+        <v>-0.5695</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2157</v>
+        <v>-2.4055</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4644</v>
+        <v>1.836</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8912</v>
+        <v>-1.8923</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4674</v>
+        <v>1.4731</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.3586</v>
+        <v>-3.3653</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1723</v>
+        <v>-1.1928</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2641</v>
+        <v>1.2583</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.4364</v>
+        <v>-2.4511</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7189</v>
+        <v>-0.6995</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2326</v>
+        <v>0.4122</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0907</v>
+        <v>-0.0746</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1418</v>
+        <v>0.4868</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.661</v>
+        <v>-1.6488</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8535</v>
+        <v>-0.7876</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8075</v>
+        <v>-0.8612</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8048</v>
+        <v>-0.8033</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9408</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.136</v>
+        <v>0.1387</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7144</v>
+        <v>-0.7179</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.0854</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O13" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0097</v>
+        <v>0.0163</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1391</v>
+        <v>-0.0697</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1488</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>30.2723</v>
+        <v>30.6233</v>
       </c>
       <c r="E14" t="n">
-        <v>18.5483</v>
+        <v>18.60299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>11.7238</v>
+        <v>12.0202</v>
       </c>
       <c r="G14" t="n">
-        <v>22.2537</v>
+        <v>22.2385</v>
       </c>
       <c r="H14" t="n">
-        <v>16.363</v>
+        <v>16.3706</v>
       </c>
       <c r="I14" t="n">
-        <v>5.890600000000001</v>
+        <v>5.8682</v>
       </c>
       <c r="J14" t="n">
-        <v>25.8701</v>
+        <v>25.6542</v>
       </c>
       <c r="K14" t="n">
-        <v>14.4891</v>
+        <v>14.3672</v>
       </c>
       <c r="L14" t="n">
-        <v>11.3811</v>
+        <v>11.2871</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.6167</v>
+        <v>-3.4157</v>
       </c>
       <c r="N14" t="n">
-        <v>1.8738</v>
+        <v>2.0034</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.4905</v>
+        <v>-5.4191</v>
       </c>
       <c r="P14" t="n">
-        <v>6.804900000000002</v>
+        <v>6.828899999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.4759</v>
+        <v>-12.5199</v>
       </c>
       <c r="R14" t="n">
-        <v>19.2809</v>
+        <v>19.3489</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4346</v>
+        <v>2.788</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.9809</v>
+        <v>-1.628</v>
       </c>
       <c r="U14" t="n">
-        <v>4.415399999999999</v>
+        <v>4.4162</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2211</v>
+        <v>-1.2324</v>
       </c>
       <c r="W14" t="n">
-        <v>7.1347</v>
+        <v>7.0966</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.3559</v>
+        <v>-8.328899999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4526</v>
+        <v>3.1217</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0103</v>
+        <v>5.3311</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5577</v>
+        <v>-2.2093</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6945</v>
+        <v>2.6942</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6234</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0711</v>
+        <v>2.0737</v>
       </c>
       <c r="J15" t="n">
-        <v>6.3633</v>
+        <v>6.3359</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7809</v>
+        <v>2.7612</v>
       </c>
       <c r="L15" t="n">
-        <v>3.5824</v>
+        <v>3.5747</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.6688</v>
+        <v>-3.6417</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.1575</v>
+        <v>-2.1406</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6276</v>
+        <v>0.0406</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7652</v>
+        <v>-0.4114</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1376</v>
+        <v>0.452</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1752</v>
+        <v>1.0031</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4299</v>
+        <v>2.2892</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2546</v>
+        <v>-1.2861</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9319</v>
+        <v>-1.9307</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.1558</v>
+        <v>-2.1542</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="J16" t="n">
-        <v>1.316</v>
+        <v>1.2953</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3605</v>
+        <v>-0.3727</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.2479</v>
+        <v>-3.226</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7953</v>
+        <v>-1.7814</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5873</v>
+        <v>0.4087</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0212</v>
+        <v>-0.0955</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5662</v>
+        <v>0.5043</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3792</v>
+        <v>0.5216</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7864</v>
+        <v>0.8903</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4072</v>
+        <v>-0.3687</v>
       </c>
       <c r="G17" t="n">
-        <v>0.201</v>
+        <v>0.1929</v>
       </c>
       <c r="H17" t="n">
         <v>0.6089</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4079</v>
+        <v>-0.416</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9951</v>
+        <v>0.981</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8139</v>
+        <v>0.8101</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1812</v>
+        <v>0.1708</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.794</v>
+        <v>-0.7881</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2755</v>
+        <v>-0.1266</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0668</v>
+        <v>-0.0359</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3788</v>
+        <v>-2.1189</v>
       </c>
       <c r="E18" t="n">
-        <v>0.846</v>
+        <v>0.6978</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2248</v>
+        <v>-2.8167</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.1205</v>
+        <v>-5.113</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9857</v>
+        <v>-1.9711</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.1347</v>
+        <v>-3.1419</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.583</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7198</v>
+        <v>-0.7382</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.5565</v>
+        <v>-4.5299</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1416</v>
+        <v>-2.1262</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.4149</v>
+        <v>-2.4037</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4437</v>
+        <v>-0.1849</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1875</v>
+        <v>-0.3046</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2562</v>
+        <v>0.1198</v>
       </c>
       <c r="V18" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>Y. PONS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5085</v>
+        <v>-2.2883</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4722</v>
+        <v>-0.2377</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0363</v>
+        <v>-2.0506</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8869</v>
+        <v>-1.7494</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4733</v>
+        <v>-1.8984</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5865</v>
+        <v>0.1489</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6425</v>
+        <v>0.945</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7171</v>
+        <v>-0.6485</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0746</v>
+        <v>1.5935</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2444</v>
+        <v>-2.6945</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7563</v>
+        <v>-1.2499</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5118</v>
+        <v>-1.4446</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1515</v>
+        <v>0.1637</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6956</v>
+        <v>-0.2023</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8471</v>
+        <v>0.3659</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-0.7025</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.92</v>
+        <v>-2.7732</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7811</v>
+        <v>-2.6808</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1389</v>
+        <v>-0.0924</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7784</v>
+        <v>-0.7744</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3867</v>
+        <v>-0.3904</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3219</v>
+        <v>0.3135</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3219</v>
+        <v>0.3135</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1003</v>
+        <v>-1.0879</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7086</v>
+        <v>-0.7039</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7806</v>
+        <v>-0.6331</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8347</v>
+        <v>-0.718</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0541</v>
+        <v>0.0849</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Y. PONS</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0229</v>
+        <v>-2.841</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5656</v>
+        <v>-2.4814</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4573</v>
+        <v>-0.3596</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7482</v>
+        <v>-0.8748</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8975</v>
+        <v>-1.4679</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1493</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9643</v>
+        <v>-0.6462</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.7207</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6019</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7125</v>
+        <v>-0.2285</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2599</v>
+        <v>-0.7472</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4526</v>
+        <v>0.5187</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5677</v>
+        <v>-0.1939</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5565</v>
+        <v>-0.697</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0112</v>
+        <v>0.5032</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>J. MCKOY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3245</v>
+        <v>-3.4433</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9988</v>
+        <v>-3.3749</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3257</v>
+        <v>-0.0684</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2085</v>
+        <v>-4.154</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0086</v>
+        <v>-3.1679</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1999</v>
+        <v>-0.9861</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3827</v>
+        <v>-2.636</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4573</v>
+        <v>-2.2483</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0746</v>
+        <v>-0.3877</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8258</v>
+        <v>-1.518</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5513</v>
+        <v>-0.9196</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2745</v>
+        <v>-0.5984</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0862</v>
+        <v>-0.6551</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3478</v>
+        <v>-0.7389</v>
       </c>
       <c r="U22" t="n">
-        <v>0.434</v>
+        <v>0.0838</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. MCKOY</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8069</v>
+        <v>-3.4819</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5903</v>
+        <v>-3.0125</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2166</v>
+        <v>-0.4694</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.1535</v>
+        <v>-1.2046</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.1673</v>
+        <v>-1.0081</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9862</v>
+        <v>-0.1965</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.6164</v>
+        <v>-0.3877</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.2379</v>
+        <v>-0.4621</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3786</v>
+        <v>0.0745</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5371</v>
+        <v>-0.8169</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9294</v>
+        <v>-0.546</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6077</v>
+        <v>-0.271</v>
       </c>
       <c r="P23" t="n">
-        <v>1.361</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0144</v>
+        <v>-0.0708</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9739</v>
+        <v>-0.3485</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0405</v>
+        <v>0.2777</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3535</v>
+        <v>-3.7439</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2164</v>
+        <v>-1.0154</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1371</v>
+        <v>-2.7285</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9712</v>
+        <v>-1.9681</v>
       </c>
       <c r="H24" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.0231</v>
+        <v>-2.0198</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8636</v>
+        <v>0.8407</v>
       </c>
       <c r="K24" t="n">
-        <v>1.6899</v>
+        <v>1.6752</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.8264</v>
+        <v>-0.8345</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.8347</v>
+        <v>-2.8087</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.638</v>
+        <v>-1.6235</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.475</v>
+        <v>-0.8653</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9043</v>
+        <v>-0.6692</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5707</v>
+        <v>-0.1961</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5306</v>
+        <v>-6.306</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5779</v>
+        <v>-3.0687</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.9528</v>
+        <v>-3.2373</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.5933</v>
+        <v>-2.5886</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7084</v>
+        <v>-1.7116</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8849</v>
+        <v>-0.877</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9466</v>
+        <v>-0.956</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.9839</v>
+        <v>-0.9932</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.6467</v>
+        <v>-1.6326</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7245</v>
+        <v>-0.7184</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6109</v>
+        <v>-0.1743</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0907</v>
+        <v>-0.3812</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5202</v>
+        <v>0.2069</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.5068</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.4333</v>
+        <v>-7.135</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.526</v>
+        <v>-6.2891</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9073</v>
+        <v>-0.8459</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.7568</v>
+        <v>-4.7681</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.8639</v>
+        <v>-3.8821</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8929</v>
+        <v>-0.886</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.0553</v>
+        <v>-2.0868</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.2419</v>
+        <v>-2.273</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.7016</v>
+        <v>-2.6813</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.6221</v>
+        <v>-1.6091</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.083</v>
+        <v>-4.0974</v>
       </c>
       <c r="Q26" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S26" t="n">
-        <v>1.3138</v>
+        <v>0.641</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9467</v>
+        <v>0.2413</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3672</v>
+        <v>0.3997</v>
       </c>
       <c r="V26" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-30.272</v>
+        <v>-29.4851</v>
       </c>
       <c r="E27" t="n">
-        <v>-12.6557</v>
+        <v>-12.9521</v>
       </c>
       <c r="F27" t="n">
-        <v>-17.6163</v>
+        <v>-16.5329</v>
       </c>
       <c r="G27" t="n">
-        <v>-22.2537</v>
+        <v>-22.2386</v>
       </c>
       <c r="H27" t="n">
-        <v>-16.3629</v>
+        <v>-16.3706</v>
       </c>
       <c r="I27" t="n">
-        <v>-5.8906</v>
+        <v>-5.8681</v>
       </c>
       <c r="J27" t="n">
-        <v>3.616700000000001</v>
+        <v>3.415699999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.873699999999999</v>
+        <v>-2.0034</v>
       </c>
       <c r="L27" t="n">
-        <v>5.490300000000001</v>
+        <v>5.419</v>
       </c>
       <c r="M27" t="n">
-        <v>-25.8703</v>
+        <v>-25.6541</v>
       </c>
       <c r="N27" t="n">
-        <v>-14.4895</v>
+        <v>-14.367</v>
       </c>
       <c r="O27" t="n">
-        <v>-11.3811</v>
+        <v>-11.2872</v>
       </c>
       <c r="P27" t="n">
-        <v>-6.8049</v>
+        <v>-6.828900000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>-19.2808</v>
+        <v>-19.3488</v>
       </c>
       <c r="R27" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.434800000000001</v>
+        <v>-1.65</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.4156</v>
+        <v>-4.415999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>1.981</v>
+        <v>2.7662</v>
       </c>
       <c r="V27" t="n">
-        <v>1.221100000000001</v>
+        <v>1.2324</v>
       </c>
       <c r="W27" t="n">
-        <v>7.423800000000001</v>
+        <v>7.3971</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.202800000000001</v>
+        <v>-6.164999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104537_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104537_W9.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.328899999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104537_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-6.164999999999999</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
